--- a/ssp_modeling/scenario_mapping/ssp_bulgaria_transformation_jan_29.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_bulgaria_transformation_jan_29.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tony/Documents/sisepuede_modeling/ssp_bulgaria/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6AA747-77A1-5843-B2A5-2B0E31078758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E033E1-BBAF-9E4A-8E28-49B758706FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5400" yWindow="1480" windowWidth="30240" windowHeight="17660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19260" yWindow="3300" windowWidth="49460" windowHeight="21340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -4401,7 +4401,9 @@
       <c r="N51" s="21">
         <v>12</v>
       </c>
-      <c r="O51" s="39"/>
+      <c r="O51" s="39">
+        <v>1</v>
+      </c>
       <c r="P51" s="39">
         <v>1.17</v>
       </c>
@@ -4591,7 +4593,9 @@
       <c r="N55" s="21">
         <v>12</v>
       </c>
-      <c r="O55" s="39"/>
+      <c r="O55" s="39">
+        <v>1</v>
+      </c>
       <c r="P55" s="39">
         <v>1</v>
       </c>
@@ -4648,7 +4652,7 @@
       </c>
       <c r="O56" s="39"/>
       <c r="P56" s="39">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="Q56" s="42">
         <v>2</v>
@@ -4701,10 +4705,10 @@
         <v>12</v>
       </c>
       <c r="O57" s="39">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="P57" s="39">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="Q57" s="42">
         <v>1</v>
@@ -4761,20 +4765,20 @@
         <v>12</v>
       </c>
       <c r="O58" s="39">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="P58" s="39">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="Q58" s="42">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="R58" s="42">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="S58" s="6">
         <f t="shared" si="1"/>
-        <v>0.93500000000000005</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="59" spans="1:21" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -4816,21 +4820,21 @@
       <c r="N59" s="21">
         <v>12</v>
       </c>
-      <c r="O59" s="40">
-        <v>0.79</v>
+      <c r="O59" s="39">
+        <v>0.71</v>
       </c>
       <c r="P59" s="39">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="Q59" s="42">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="R59" s="42">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="S59" s="6">
         <f t="shared" si="1"/>
-        <v>0.93500000000000005</v>
+        <v>0.85</v>
       </c>
       <c r="T59"/>
       <c r="U59"/>
@@ -4875,20 +4879,20 @@
         <v>12</v>
       </c>
       <c r="O60" s="39">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="P60" s="39">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="Q60" s="42">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="R60" s="42">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="S60" s="6">
         <f t="shared" si="1"/>
-        <v>0.93500000000000005</v>
+        <v>0.85</v>
       </c>
       <c r="T60"/>
       <c r="U60"/>
@@ -4929,10 +4933,10 @@
         <v>12</v>
       </c>
       <c r="O61" s="39">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="P61" s="39">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="Q61" s="42">
         <v>1</v>
@@ -4991,10 +4995,10 @@
         <v>12</v>
       </c>
       <c r="O62" s="39">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="P62" s="39">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="Q62" s="42">
         <v>1</v>

--- a/ssp_modeling/scenario_mapping/ssp_bulgaria_transformation_jan_29.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_bulgaria_transformation_jan_29.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tony/Documents/sisepuede_modeling/ssp_bulgaria/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E033E1-BBAF-9E4A-8E28-49B758706FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF22D71E-4886-E847-950F-A43392CCC096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19260" yWindow="3300" windowWidth="49460" windowHeight="21340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3198,7 +3198,7 @@
         <v>0.15</v>
       </c>
       <c r="Q24" s="42">
-        <v>0.78</v>
+        <v>1.38</v>
       </c>
       <c r="R24" s="42">
         <v>1.38</v>
@@ -5111,8 +5111,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R1048576">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="O1:R1048576">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5123,8 +5123,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O1:R1048576">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="R1:R1048576">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
